--- a/data.xlsx
+++ b/data.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="24334"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30131"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\■개인폴더\박경태\역사위치안내(github)\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Musicat\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FB578691-7BCB-4DE9-9ADE-447609869C5A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EFA2E1F1-DF39-4E71-BB78-A7ED2E0C10C8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{21F0DF5A-062E-4FED-9C31-648F525201B8}"/>
+    <workbookView xWindow="-105" yWindow="0" windowWidth="14610" windowHeight="15585" xr2:uid="{21F0DF5A-062E-4FED-9C31-648F525201B8}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -30,15 +30,12 @@
         <xcalcf:feature name="microsoft.com:LET_WF"/>
       </xcalcf:calcFeatures>
     </ext>
-    <ext xmlns:xlwcv="http://schemas.microsoft.com/office/spreadsheetml/2024/workbookCompatibilityVersion" uri="{D14903EA-33C4-47F7-8F05-3474C54BE107}">
-      <xlwcv:version setVersion="1"/>
-    </ext>
   </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="869" uniqueCount="372">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="889" uniqueCount="378">
   <si>
     <t>연번</t>
     <phoneticPr fontId="2" type="noConversion"/>
@@ -1308,6 +1305,27 @@
   </si>
   <si>
     <t>2번 출구</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>3번 출구</t>
+  </si>
+  <si>
+    <t>4번 출구</t>
+  </si>
+  <si>
+    <t>1번 출구</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>2번 출구</t>
+  </si>
+  <si>
+    <t>화장실</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>032-451-4310</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
 </sst>
@@ -1391,13 +1409,13 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="176" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -1419,9 +1437,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 테마">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 2013 - 2022 테마">
   <a:themeElements>
-    <a:clrScheme name="Office">
+    <a:clrScheme name="Office 2013 - 2022">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -1459,7 +1477,7 @@
         <a:srgbClr val="954F72"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office">
+    <a:fontScheme name="Office 2013 - 2022">
       <a:majorFont>
         <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
@@ -1565,7 +1583,7 @@
         <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office">
+    <a:fmtScheme name="Office 2013 - 2022">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -1707,7 +1725,7 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office 2013 - 2022 Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
@@ -1715,7 +1733,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{98156557-3AEA-41A3-9863-FC7FAA63B0F4}">
-  <dimension ref="A1:X82"/>
+  <dimension ref="A1:X87"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="5.25" style="1" bestFit="1" customWidth="1"/>
@@ -1748,19 +1766,19 @@
       <c r="E1" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="6" t="s">
+      <c r="F1" s="5" t="s">
         <v>195</v>
       </c>
-      <c r="G1" s="7" t="s">
+      <c r="G1" s="6" t="s">
         <v>5</v>
       </c>
-      <c r="H1" s="6" t="s">
+      <c r="H1" s="5" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="6" t="s">
+      <c r="I1" s="5" t="s">
         <v>8</v>
       </c>
-      <c r="J1" s="6" t="s">
+      <c r="J1" s="5" t="s">
         <v>6</v>
       </c>
       <c r="K1" s="1" t="s">
@@ -1803,7 +1821,7 @@
         <v>11</v>
       </c>
       <c r="J2" s="1" t="str">
-        <f>B2&amp;E2</f>
+        <f t="shared" ref="J2:J49" si="0">B2&amp;E2</f>
         <v>211ZONE08</v>
       </c>
       <c r="K2" s="1" t="str">
@@ -1817,7 +1835,7 @@
     </row>
     <row r="3" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A3" s="1">
-        <f t="shared" ref="A3:A66" si="0">ROW()-1</f>
+        <f t="shared" ref="A3:A66" si="1">ROW()-1</f>
         <v>2</v>
       </c>
       <c r="B3" s="1">
@@ -1837,7 +1855,7 @@
         <v>가정역</v>
       </c>
       <c r="G3" s="2" t="str">
-        <f t="shared" ref="G3:G66" si="1">B3&amp;C3&amp;TEXT(D3,"000")</f>
+        <f t="shared" ref="G3:G66" si="2">B3&amp;C3&amp;TEXT(D3,"000")</f>
         <v>211ES002</v>
       </c>
       <c r="H3" s="1" t="s">
@@ -1847,11 +1865,11 @@
         <v>11</v>
       </c>
       <c r="J3" s="1" t="str">
-        <f>B3&amp;E3</f>
+        <f t="shared" si="0"/>
         <v>211ZONE14</v>
       </c>
       <c r="K3" s="1" t="str">
-        <f t="shared" ref="K3:L66" si="2">"https://2line.pages.dev/?id="&amp;G3&amp;","&amp;G3</f>
+        <f t="shared" ref="K3:K66" si="3">"https://2line.pages.dev/?id="&amp;G3&amp;","&amp;G3</f>
         <v>https://2line.pages.dev/?id=211ES002,211ES002</v>
       </c>
       <c r="L3" s="3" t="s">
@@ -1861,7 +1879,7 @@
     </row>
     <row r="4" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A4" s="1">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>3</v>
       </c>
       <c r="B4" s="1">
@@ -1881,7 +1899,7 @@
         <v>가정역</v>
       </c>
       <c r="G4" s="2" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>211ES003</v>
       </c>
       <c r="H4" s="1" t="s">
@@ -1891,11 +1909,11 @@
         <v>11</v>
       </c>
       <c r="J4" s="1" t="str">
-        <f>B4&amp;E4</f>
+        <f t="shared" si="0"/>
         <v>211ZONE07</v>
       </c>
       <c r="K4" s="1" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>https://2line.pages.dev/?id=211ES003,211ES003</v>
       </c>
       <c r="L4" s="3" t="s">
@@ -1905,7 +1923,7 @@
     </row>
     <row r="5" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A5" s="1">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>4</v>
       </c>
       <c r="B5" s="1">
@@ -1925,7 +1943,7 @@
         <v>가정역</v>
       </c>
       <c r="G5" s="2" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>211ES004</v>
       </c>
       <c r="H5" s="1" t="s">
@@ -1935,11 +1953,11 @@
         <v>11</v>
       </c>
       <c r="J5" s="1" t="str">
-        <f>B5&amp;E5</f>
+        <f t="shared" si="0"/>
         <v>211ZONE12</v>
       </c>
       <c r="K5" s="1" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>https://2line.pages.dev/?id=211ES004,211ES004</v>
       </c>
       <c r="L5" s="3" t="s">
@@ -1949,7 +1967,7 @@
     </row>
     <row r="6" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A6" s="1">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>5</v>
       </c>
       <c r="B6" s="1">
@@ -1969,7 +1987,7 @@
         <v>가정역</v>
       </c>
       <c r="G6" s="2" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>211ES005</v>
       </c>
       <c r="H6" s="1" t="s">
@@ -1979,11 +1997,11 @@
         <v>11</v>
       </c>
       <c r="J6" s="1" t="str">
-        <f>B6&amp;E6</f>
+        <f t="shared" si="0"/>
         <v>211ZONE07</v>
       </c>
       <c r="K6" s="1" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>https://2line.pages.dev/?id=211ES005,211ES005</v>
       </c>
       <c r="L6" s="3" t="s">
@@ -1993,7 +2011,7 @@
     </row>
     <row r="7" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A7" s="1">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>6</v>
       </c>
       <c r="B7" s="1">
@@ -2013,7 +2031,7 @@
         <v>가정역</v>
       </c>
       <c r="G7" s="2" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>211ES006</v>
       </c>
       <c r="H7" s="1" t="s">
@@ -2023,11 +2041,11 @@
         <v>11</v>
       </c>
       <c r="J7" s="1" t="str">
-        <f>B7&amp;E7</f>
+        <f t="shared" si="0"/>
         <v>211ZONE09</v>
       </c>
       <c r="K7" s="1" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>https://2line.pages.dev/?id=211ES006,211ES006</v>
       </c>
       <c r="L7" s="3" t="s">
@@ -2038,7 +2056,7 @@
     </row>
     <row r="8" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A8" s="1">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>7</v>
       </c>
       <c r="B8" s="1">
@@ -2058,7 +2076,7 @@
         <v>가정역</v>
       </c>
       <c r="G8" s="2" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>211ES007</v>
       </c>
       <c r="H8" s="1" t="s">
@@ -2068,11 +2086,11 @@
         <v>11</v>
       </c>
       <c r="J8" s="1" t="str">
-        <f>B8&amp;E8</f>
+        <f t="shared" si="0"/>
         <v>211ZONE08</v>
       </c>
       <c r="K8" s="1" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>https://2line.pages.dev/?id=211ES007,211ES007</v>
       </c>
       <c r="L8" s="3" t="s">
@@ -2082,7 +2100,7 @@
     </row>
     <row r="9" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A9" s="1">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>8</v>
       </c>
       <c r="B9" s="1">
@@ -2102,7 +2120,7 @@
         <v>가정역</v>
       </c>
       <c r="G9" s="2" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>211ES008</v>
       </c>
       <c r="H9" s="1" t="s">
@@ -2112,11 +2130,11 @@
         <v>11</v>
       </c>
       <c r="J9" s="1" t="str">
-        <f>B9&amp;E9</f>
+        <f t="shared" si="0"/>
         <v>211ZONE11</v>
       </c>
       <c r="K9" s="1" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>https://2line.pages.dev/?id=211ES008,211ES008</v>
       </c>
       <c r="L9" s="3" t="s">
@@ -2126,7 +2144,7 @@
     </row>
     <row r="10" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A10" s="1">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>9</v>
       </c>
       <c r="B10" s="1">
@@ -2146,7 +2164,7 @@
         <v>가정역</v>
       </c>
       <c r="G10" s="2" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>211ES009</v>
       </c>
       <c r="H10" s="1" t="s">
@@ -2156,11 +2174,11 @@
         <v>11</v>
       </c>
       <c r="J10" s="1" t="str">
-        <f>B10&amp;E10</f>
+        <f t="shared" si="0"/>
         <v>211ZONE08</v>
       </c>
       <c r="K10" s="1" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>https://2line.pages.dev/?id=211ES009,211ES009</v>
       </c>
       <c r="L10" s="3" t="s">
@@ -2170,7 +2188,7 @@
     </row>
     <row r="11" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A11" s="1">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>10</v>
       </c>
       <c r="B11" s="1">
@@ -2190,7 +2208,7 @@
         <v>가정역</v>
       </c>
       <c r="G11" s="2" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>211ES010</v>
       </c>
       <c r="H11" s="1" t="s">
@@ -2200,11 +2218,11 @@
         <v>11</v>
       </c>
       <c r="J11" s="1" t="str">
-        <f>B11&amp;E11</f>
+        <f t="shared" si="0"/>
         <v>211ZONE08</v>
       </c>
       <c r="K11" s="1" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>https://2line.pages.dev/?id=211ES010,211ES010</v>
       </c>
       <c r="L11" s="3" t="s">
@@ -2214,7 +2232,7 @@
     </row>
     <row r="12" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A12" s="1">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>11</v>
       </c>
       <c r="B12" s="1">
@@ -2234,7 +2252,7 @@
         <v>가정역</v>
       </c>
       <c r="G12" s="2" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>211ES011</v>
       </c>
       <c r="H12" s="1" t="s">
@@ -2244,11 +2262,11 @@
         <v>11</v>
       </c>
       <c r="J12" s="1" t="str">
-        <f>B12&amp;E12</f>
+        <f t="shared" si="0"/>
         <v>211ZONE07</v>
       </c>
       <c r="K12" s="1" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>https://2line.pages.dev/?id=211ES011,211ES011</v>
       </c>
       <c r="L12" s="3" t="s">
@@ -2258,7 +2276,7 @@
     </row>
     <row r="13" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A13" s="1">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>12</v>
       </c>
       <c r="B13" s="1">
@@ -2278,7 +2296,7 @@
         <v>가정역</v>
       </c>
       <c r="G13" s="2" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>211ES012</v>
       </c>
       <c r="H13" s="1" t="s">
@@ -2288,11 +2306,11 @@
         <v>11</v>
       </c>
       <c r="J13" s="1" t="str">
-        <f>B13&amp;E13</f>
+        <f t="shared" si="0"/>
         <v>211ZONE07</v>
       </c>
       <c r="K13" s="1" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>https://2line.pages.dev/?id=211ES012,211ES012</v>
       </c>
       <c r="L13" s="3" t="s">
@@ -2302,7 +2320,7 @@
     </row>
     <row r="14" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A14" s="1">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>13</v>
       </c>
       <c r="B14" s="1">
@@ -2322,7 +2340,7 @@
         <v>가정역</v>
       </c>
       <c r="G14" s="2" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>211ES013</v>
       </c>
       <c r="H14" s="1" t="s">
@@ -2332,11 +2350,11 @@
         <v>11</v>
       </c>
       <c r="J14" s="1" t="str">
-        <f>B14&amp;E14</f>
+        <f t="shared" si="0"/>
         <v>211ZONE02</v>
       </c>
       <c r="K14" s="1" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>https://2line.pages.dev/?id=211ES013,211ES013</v>
       </c>
       <c r="L14" s="3" t="s">
@@ -2346,7 +2364,7 @@
     </row>
     <row r="15" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A15" s="1">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>14</v>
       </c>
       <c r="B15" s="1">
@@ -2366,7 +2384,7 @@
         <v>가정역</v>
       </c>
       <c r="G15" s="2" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>211ES014</v>
       </c>
       <c r="H15" s="1" t="s">
@@ -2376,11 +2394,11 @@
         <v>11</v>
       </c>
       <c r="J15" s="1" t="str">
-        <f>B15&amp;E15</f>
+        <f t="shared" si="0"/>
         <v>211ZONE02</v>
       </c>
       <c r="K15" s="1" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>https://2line.pages.dev/?id=211ES014,211ES014</v>
       </c>
       <c r="L15" s="3" t="s">
@@ -2390,7 +2408,7 @@
     </row>
     <row r="16" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A16" s="1">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>15</v>
       </c>
       <c r="B16" s="1">
@@ -2410,7 +2428,7 @@
         <v>가정역</v>
       </c>
       <c r="G16" s="2" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>211ES015</v>
       </c>
       <c r="H16" s="1" t="s">
@@ -2420,11 +2438,11 @@
         <v>11</v>
       </c>
       <c r="J16" s="1" t="str">
-        <f>B16&amp;E16</f>
+        <f t="shared" si="0"/>
         <v>211ZONE05</v>
       </c>
       <c r="K16" s="1" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>https://2line.pages.dev/?id=211ES015,211ES015</v>
       </c>
       <c r="L16" s="3" t="s">
@@ -2434,7 +2452,7 @@
     </row>
     <row r="17" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A17" s="1">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>16</v>
       </c>
       <c r="B17" s="1">
@@ -2454,7 +2472,7 @@
         <v>가정역</v>
       </c>
       <c r="G17" s="2" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>211ES016</v>
       </c>
       <c r="H17" s="1" t="s">
@@ -2464,11 +2482,11 @@
         <v>11</v>
       </c>
       <c r="J17" s="1" t="str">
-        <f>B17&amp;E17</f>
+        <f t="shared" si="0"/>
         <v>211ZONE05</v>
       </c>
       <c r="K17" s="1" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>https://2line.pages.dev/?id=211ES016,211ES016</v>
       </c>
       <c r="L17" s="3" t="s">
@@ -2478,7 +2496,7 @@
     </row>
     <row r="18" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A18" s="1">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>17</v>
       </c>
       <c r="B18" s="1">
@@ -2498,7 +2516,7 @@
         <v>가정역</v>
       </c>
       <c r="G18" s="2" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>211ES017</v>
       </c>
       <c r="H18" s="1" t="s">
@@ -2508,11 +2526,11 @@
         <v>11</v>
       </c>
       <c r="J18" s="1" t="str">
-        <f>B18&amp;E18</f>
+        <f t="shared" si="0"/>
         <v>211ZONE01</v>
       </c>
       <c r="K18" s="1" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>https://2line.pages.dev/?id=211ES017,211ES017</v>
       </c>
       <c r="L18" s="3" t="s">
@@ -2522,7 +2540,7 @@
     </row>
     <row r="19" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A19" s="1">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>18</v>
       </c>
       <c r="B19" s="1">
@@ -2542,7 +2560,7 @@
         <v>가정역</v>
       </c>
       <c r="G19" s="2" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>211ES018</v>
       </c>
       <c r="H19" s="1" t="s">
@@ -2552,11 +2570,11 @@
         <v>11</v>
       </c>
       <c r="J19" s="1" t="str">
-        <f>B19&amp;E19</f>
+        <f t="shared" si="0"/>
         <v>211ZONE01</v>
       </c>
       <c r="K19" s="1" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>https://2line.pages.dev/?id=211ES018,211ES018</v>
       </c>
       <c r="L19" s="3" t="s">
@@ -2566,7 +2584,7 @@
     </row>
     <row r="20" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A20" s="1">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>19</v>
       </c>
       <c r="B20" s="1">
@@ -2586,7 +2604,7 @@
         <v>가정역</v>
       </c>
       <c r="G20" s="2" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>211EL001</v>
       </c>
       <c r="H20" s="1" t="s">
@@ -2596,11 +2614,11 @@
         <v>11</v>
       </c>
       <c r="J20" s="1" t="str">
-        <f>B20&amp;E20</f>
+        <f t="shared" si="0"/>
         <v>211ZONE02</v>
       </c>
       <c r="K20" s="1" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>https://2line.pages.dev/?id=211EL001,211EL001</v>
       </c>
       <c r="L20" s="3" t="s">
@@ -2610,7 +2628,7 @@
     </row>
     <row r="21" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A21" s="1">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>20</v>
       </c>
       <c r="B21" s="1">
@@ -2630,7 +2648,7 @@
         <v>가정역</v>
       </c>
       <c r="G21" s="2" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>211EL002</v>
       </c>
       <c r="H21" s="1" t="s">
@@ -2640,11 +2658,11 @@
         <v>11</v>
       </c>
       <c r="J21" s="1" t="str">
-        <f>B21&amp;E21</f>
+        <f t="shared" si="0"/>
         <v>211ZONE05</v>
       </c>
       <c r="K21" s="1" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>https://2line.pages.dev/?id=211EL002,211EL002</v>
       </c>
       <c r="L21" s="3" t="s">
@@ -2654,7 +2672,7 @@
     </row>
     <row r="22" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A22" s="1">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>21</v>
       </c>
       <c r="B22" s="1">
@@ -2674,7 +2692,7 @@
         <v>가정역</v>
       </c>
       <c r="G22" s="2" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>211EL003</v>
       </c>
       <c r="H22" s="1" t="s">
@@ -2684,11 +2702,11 @@
         <v>11</v>
       </c>
       <c r="J22" s="1" t="str">
-        <f>B22&amp;E22</f>
+        <f t="shared" si="0"/>
         <v>211ZONE05</v>
       </c>
       <c r="K22" s="1" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>https://2line.pages.dev/?id=211EL003,211EL003</v>
       </c>
       <c r="L22" s="3" t="s">
@@ -2698,7 +2716,7 @@
     </row>
     <row r="23" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A23" s="1">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>22</v>
       </c>
       <c r="B23" s="1">
@@ -2718,7 +2736,7 @@
         <v>가정역</v>
       </c>
       <c r="G23" s="2" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>211EL004</v>
       </c>
       <c r="H23" s="1" t="s">
@@ -2728,11 +2746,11 @@
         <v>11</v>
       </c>
       <c r="J23" s="1" t="str">
-        <f>B23&amp;E23</f>
+        <f t="shared" si="0"/>
         <v>211ZONE02</v>
       </c>
       <c r="K23" s="1" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>https://2line.pages.dev/?id=211EL004,211EL004</v>
       </c>
       <c r="L23" s="3" t="s">
@@ -2742,7 +2760,7 @@
     </row>
     <row r="24" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A24" s="1">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>23</v>
       </c>
       <c r="B24" s="1">
@@ -2762,7 +2780,7 @@
         <v>가정역</v>
       </c>
       <c r="G24" s="2" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>211EL005</v>
       </c>
       <c r="H24" s="1" t="s">
@@ -2772,11 +2790,11 @@
         <v>11</v>
       </c>
       <c r="J24" s="1" t="str">
-        <f>B24&amp;E24</f>
+        <f t="shared" si="0"/>
         <v>211ZONE02</v>
       </c>
       <c r="K24" s="1" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>https://2line.pages.dev/?id=211EL005,211EL005</v>
       </c>
       <c r="L24" s="3" t="s">
@@ -2786,7 +2804,7 @@
     </row>
     <row r="25" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A25" s="1">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>24</v>
       </c>
       <c r="B25" s="1">
@@ -2806,7 +2824,7 @@
         <v>가정역</v>
       </c>
       <c r="G25" s="2" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>211EL006</v>
       </c>
       <c r="H25" s="1" t="s">
@@ -2816,11 +2834,11 @@
         <v>11</v>
       </c>
       <c r="J25" s="1" t="str">
-        <f>B25&amp;E25</f>
+        <f t="shared" si="0"/>
         <v>211ZONE02</v>
       </c>
       <c r="K25" s="1" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>https://2line.pages.dev/?id=211EL006,211EL006</v>
       </c>
       <c r="L25" s="3" t="s">
@@ -2830,7 +2848,7 @@
     </row>
     <row r="26" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A26" s="1">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>25</v>
       </c>
       <c r="B26" s="1">
@@ -2850,7 +2868,7 @@
         <v>가정역</v>
       </c>
       <c r="G26" s="2" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>211EL007</v>
       </c>
       <c r="H26" s="1" t="s">
@@ -2860,11 +2878,11 @@
         <v>11</v>
       </c>
       <c r="J26" s="1" t="str">
-        <f>B26&amp;E26</f>
+        <f t="shared" si="0"/>
         <v>211ZONE13</v>
       </c>
       <c r="K26" s="1" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>https://2line.pages.dev/?id=211EL007,211EL007</v>
       </c>
       <c r="L26" s="3" t="s">
@@ -2874,7 +2892,7 @@
     </row>
     <row r="27" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A27" s="1">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>26</v>
       </c>
       <c r="B27" s="1">
@@ -2894,7 +2912,7 @@
         <v>가정역</v>
       </c>
       <c r="G27" s="2" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>211EL008</v>
       </c>
       <c r="H27" s="1" t="s">
@@ -2904,11 +2922,11 @@
         <v>11</v>
       </c>
       <c r="J27" s="1" t="str">
-        <f>B27&amp;E27</f>
+        <f t="shared" si="0"/>
         <v>211ZONE13</v>
       </c>
       <c r="K27" s="1" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>https://2line.pages.dev/?id=211EL008,211EL008</v>
       </c>
       <c r="L27" s="3" t="s">
@@ -2918,7 +2936,7 @@
     </row>
     <row r="28" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A28" s="1">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>27</v>
       </c>
       <c r="B28" s="1">
@@ -2938,7 +2956,7 @@
         <v>가정역</v>
       </c>
       <c r="G28" s="2" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>211EL009</v>
       </c>
       <c r="H28" s="1" t="s">
@@ -2948,11 +2966,11 @@
         <v>11</v>
       </c>
       <c r="J28" s="1" t="str">
-        <f>B28&amp;E28</f>
+        <f t="shared" si="0"/>
         <v>211ZONE10</v>
       </c>
       <c r="K28" s="1" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>https://2line.pages.dev/?id=211EL009,211EL009</v>
       </c>
       <c r="L28" s="3" t="s">
@@ -2962,7 +2980,7 @@
     </row>
     <row r="29" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A29" s="1">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>28</v>
       </c>
       <c r="B29" s="1">
@@ -2982,7 +3000,7 @@
         <v>가정역</v>
       </c>
       <c r="G29" s="2" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>211EL010</v>
       </c>
       <c r="H29" s="1" t="s">
@@ -2992,11 +3010,11 @@
         <v>11</v>
       </c>
       <c r="J29" s="1" t="str">
-        <f>B29&amp;E29</f>
+        <f t="shared" si="0"/>
         <v>211ZONE10</v>
       </c>
       <c r="K29" s="1" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>https://2line.pages.dev/?id=211EL010,211EL010</v>
       </c>
       <c r="L29" s="3" t="s">
@@ -3006,7 +3024,7 @@
     </row>
     <row r="30" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A30" s="1">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>29</v>
       </c>
       <c r="B30" s="1">
@@ -3026,7 +3044,7 @@
         <v>가정역</v>
       </c>
       <c r="G30" s="2" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>211EXIT001</v>
       </c>
       <c r="H30" s="1" t="s">
@@ -3036,11 +3054,11 @@
         <v>11</v>
       </c>
       <c r="J30" s="1" t="str">
-        <f>B30&amp;E30</f>
+        <f t="shared" si="0"/>
         <v>211ZONE03</v>
       </c>
       <c r="K30" s="1" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>https://2line.pages.dev/?id=211EXIT001,211EXIT001</v>
       </c>
       <c r="L30" s="3" t="s">
@@ -3050,7 +3068,7 @@
     </row>
     <row r="31" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A31" s="1">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>30</v>
       </c>
       <c r="B31" s="1">
@@ -3070,7 +3088,7 @@
         <v>가정역</v>
       </c>
       <c r="G31" s="2" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>211EXIT002</v>
       </c>
       <c r="H31" s="1" t="s">
@@ -3080,11 +3098,11 @@
         <v>11</v>
       </c>
       <c r="J31" s="1" t="str">
-        <f>B31&amp;E31</f>
+        <f t="shared" si="0"/>
         <v>211ZONE06</v>
       </c>
       <c r="K31" s="1" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>https://2line.pages.dev/?id=211EXIT002,211EXIT002</v>
       </c>
       <c r="L31" s="3" t="s">
@@ -3094,7 +3112,7 @@
     </row>
     <row r="32" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A32" s="1">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>31</v>
       </c>
       <c r="B32" s="1">
@@ -3114,7 +3132,7 @@
         <v>가정역</v>
       </c>
       <c r="G32" s="2" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>211EXIT003</v>
       </c>
       <c r="H32" s="1" t="s">
@@ -3124,11 +3142,11 @@
         <v>11</v>
       </c>
       <c r="J32" s="1" t="str">
-        <f>B32&amp;E32</f>
+        <f t="shared" si="0"/>
         <v>211ZONE06</v>
       </c>
       <c r="K32" s="1" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>https://2line.pages.dev/?id=211EXIT003,211EXIT003</v>
       </c>
       <c r="L32" s="3" t="s">
@@ -3138,7 +3156,7 @@
     </row>
     <row r="33" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A33" s="1">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>32</v>
       </c>
       <c r="B33" s="1">
@@ -3158,7 +3176,7 @@
         <v>가정역</v>
       </c>
       <c r="G33" s="2" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>211EXIT004</v>
       </c>
       <c r="H33" s="1" t="s">
@@ -3168,11 +3186,11 @@
         <v>11</v>
       </c>
       <c r="J33" s="1" t="str">
-        <f>B33&amp;E33</f>
+        <f t="shared" si="0"/>
         <v>211ZONE04</v>
       </c>
       <c r="K33" s="1" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>https://2line.pages.dev/?id=211EXIT004,211EXIT004</v>
       </c>
       <c r="L33" s="3" t="s">
@@ -3182,7 +3200,7 @@
     </row>
     <row r="34" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A34" s="1">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>33</v>
       </c>
       <c r="B34" s="1">
@@ -3202,7 +3220,7 @@
         <v>가정역</v>
       </c>
       <c r="G34" s="2" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>211EXIT005</v>
       </c>
       <c r="H34" s="1" t="s">
@@ -3212,11 +3230,11 @@
         <v>11</v>
       </c>
       <c r="J34" s="1" t="str">
-        <f>B34&amp;E34</f>
+        <f t="shared" si="0"/>
         <v>211ZONE04</v>
       </c>
       <c r="K34" s="1" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>https://2line.pages.dev/?id=211EXIT005,211EXIT005</v>
       </c>
       <c r="L34" s="3" t="s">
@@ -3226,7 +3244,7 @@
     </row>
     <row r="35" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A35" s="1">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>34</v>
       </c>
       <c r="B35" s="1">
@@ -3246,7 +3264,7 @@
         <v>가정역</v>
       </c>
       <c r="G35" s="2" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>211EXIT006</v>
       </c>
       <c r="H35" s="1" t="s">
@@ -3256,11 +3274,11 @@
         <v>11</v>
       </c>
       <c r="J35" s="1" t="str">
-        <f>B35&amp;E35</f>
+        <f t="shared" si="0"/>
         <v>211ZONE01</v>
       </c>
       <c r="K35" s="1" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>https://2line.pages.dev/?id=211EXIT006,211EXIT006</v>
       </c>
       <c r="L35" s="3" t="s">
@@ -3270,7 +3288,7 @@
     </row>
     <row r="36" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A36" s="1">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>35</v>
       </c>
       <c r="B36" s="1">
@@ -3290,7 +3308,7 @@
         <v>가정역</v>
       </c>
       <c r="G36" s="2" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>211EXIT007</v>
       </c>
       <c r="H36" s="1" t="s">
@@ -3300,11 +3318,11 @@
         <v>11</v>
       </c>
       <c r="J36" s="1" t="str">
-        <f>B36&amp;E36</f>
+        <f t="shared" si="0"/>
         <v>211ZONE01</v>
       </c>
       <c r="K36" s="1" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>https://2line.pages.dev/?id=211EXIT007,211EXIT007</v>
       </c>
       <c r="L36" s="3" t="s">
@@ -3314,7 +3332,7 @@
     </row>
     <row r="37" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A37" s="1">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>36</v>
       </c>
       <c r="B37" s="1">
@@ -3334,7 +3352,7 @@
         <v>가정역</v>
       </c>
       <c r="G37" s="2" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>211EXIT008</v>
       </c>
       <c r="H37" s="1" t="s">
@@ -3344,11 +3362,11 @@
         <v>11</v>
       </c>
       <c r="J37" s="1" t="str">
-        <f>B37&amp;E37</f>
+        <f t="shared" si="0"/>
         <v>211ZONE03</v>
       </c>
       <c r="K37" s="1" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>https://2line.pages.dev/?id=211EXIT008,211EXIT008</v>
       </c>
       <c r="L37" s="3" t="s">
@@ -3358,7 +3376,7 @@
     </row>
     <row r="38" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A38" s="1">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>37</v>
       </c>
       <c r="B38" s="1">
@@ -3378,7 +3396,7 @@
         <v>가정역</v>
       </c>
       <c r="G38" s="2" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>211TOILET6M</v>
       </c>
       <c r="H38" s="1" t="s">
@@ -3388,11 +3406,11 @@
         <v>11</v>
       </c>
       <c r="J38" s="1" t="str">
-        <f>B38&amp;E38</f>
+        <f t="shared" si="0"/>
         <v>211ZONE01</v>
       </c>
       <c r="K38" s="1" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>https://2line.pages.dev/?id=211TOILET6M,211TOILET6M</v>
       </c>
       <c r="L38" s="3" t="s">
@@ -3402,7 +3420,7 @@
     </row>
     <row r="39" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A39" s="1">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>38</v>
       </c>
       <c r="B39" s="1">
@@ -3422,7 +3440,7 @@
         <v>가정역</v>
       </c>
       <c r="G39" s="2" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>211TOILET6W</v>
       </c>
       <c r="H39" s="1" t="s">
@@ -3432,11 +3450,11 @@
         <v>11</v>
       </c>
       <c r="J39" s="1" t="str">
-        <f>B39&amp;E39</f>
+        <f t="shared" si="0"/>
         <v>211ZONE01</v>
       </c>
       <c r="K39" s="1" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>https://2line.pages.dev/?id=211TOILET6W,211TOILET6W</v>
       </c>
       <c r="L39" s="3" t="s">
@@ -3446,7 +3464,7 @@
     </row>
     <row r="40" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A40" s="1">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>39</v>
       </c>
       <c r="B40" s="1">
@@ -3466,7 +3484,7 @@
         <v>가정역</v>
       </c>
       <c r="G40" s="2" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>211TOILET5M</v>
       </c>
       <c r="H40" s="1" t="s">
@@ -3476,11 +3494,11 @@
         <v>11</v>
       </c>
       <c r="J40" s="1" t="str">
-        <f>B40&amp;E40</f>
+        <f t="shared" si="0"/>
         <v>211ZONE04</v>
       </c>
       <c r="K40" s="1" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>https://2line.pages.dev/?id=211TOILET5M,211TOILET5M</v>
       </c>
       <c r="L40" s="3" t="s">
@@ -3490,7 +3508,7 @@
     </row>
     <row r="41" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A41" s="1">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>40</v>
       </c>
       <c r="B41" s="1">
@@ -3510,7 +3528,7 @@
         <v>가정역</v>
       </c>
       <c r="G41" s="2" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>211TOILET5W</v>
       </c>
       <c r="H41" s="1" t="s">
@@ -3520,11 +3538,11 @@
         <v>11</v>
       </c>
       <c r="J41" s="1" t="str">
-        <f>B41&amp;E41</f>
+        <f t="shared" si="0"/>
         <v>211ZONE04</v>
       </c>
       <c r="K41" s="1" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>https://2line.pages.dev/?id=211TOILET5W,211TOILET5W</v>
       </c>
       <c r="L41" s="3" t="s">
@@ -3534,7 +3552,7 @@
     </row>
     <row r="42" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A42" s="1">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>41</v>
       </c>
       <c r="B42" s="1">
@@ -3554,7 +3572,7 @@
         <v>가정역</v>
       </c>
       <c r="G42" s="2" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>211UPFRONT</v>
       </c>
       <c r="H42" s="1" t="s">
@@ -3564,11 +3582,11 @@
         <v>11</v>
       </c>
       <c r="J42" s="1" t="str">
-        <f>B42&amp;E42</f>
+        <f t="shared" si="0"/>
         <v>211ZONE14</v>
       </c>
       <c r="K42" s="1" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>https://2line.pages.dev/?id=211UPFRONT,211UPFRONT</v>
       </c>
       <c r="L42" s="3" t="s">
@@ -3578,7 +3596,7 @@
     </row>
     <row r="43" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A43" s="1">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>42</v>
       </c>
       <c r="B43" s="1">
@@ -3598,7 +3616,7 @@
         <v>가정역</v>
       </c>
       <c r="G43" s="2" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>211UPMID</v>
       </c>
       <c r="H43" s="1" t="s">
@@ -3608,11 +3626,11 @@
         <v>11</v>
       </c>
       <c r="J43" s="1" t="str">
-        <f>B43&amp;E43</f>
+        <f t="shared" si="0"/>
         <v>211ZONE13</v>
       </c>
       <c r="K43" s="1" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>https://2line.pages.dev/?id=211UPMID,211UPMID</v>
       </c>
       <c r="L43" s="3" t="s">
@@ -3622,7 +3640,7 @@
     </row>
     <row r="44" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A44" s="1">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>43</v>
       </c>
       <c r="B44" s="1">
@@ -3642,7 +3660,7 @@
         <v>가정역</v>
       </c>
       <c r="G44" s="2" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>211UPREAR</v>
       </c>
       <c r="H44" s="1" t="s">
@@ -3652,11 +3670,11 @@
         <v>11</v>
       </c>
       <c r="J44" s="1" t="str">
-        <f>B44&amp;E44</f>
+        <f t="shared" si="0"/>
         <v>211ZONE12</v>
       </c>
       <c r="K44" s="1" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>https://2line.pages.dev/?id=211UPREAR,211UPREAR</v>
       </c>
       <c r="L44" s="3" t="s">
@@ -3666,7 +3684,7 @@
     </row>
     <row r="45" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A45" s="1">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>44</v>
       </c>
       <c r="B45" s="1">
@@ -3686,7 +3704,7 @@
         <v>가정역</v>
       </c>
       <c r="G45" s="2" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>211DOWNFRONT</v>
       </c>
       <c r="H45" s="1" t="s">
@@ -3696,11 +3714,11 @@
         <v>11</v>
       </c>
       <c r="J45" s="1" t="str">
-        <f>B45&amp;E45</f>
+        <f t="shared" si="0"/>
         <v>211ZONE09</v>
       </c>
       <c r="K45" s="1" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>https://2line.pages.dev/?id=211DOWNFRONT,211DOWNFRONT</v>
       </c>
       <c r="L45" s="3" t="s">
@@ -3710,7 +3728,7 @@
     </row>
     <row r="46" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A46" s="1">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>45</v>
       </c>
       <c r="B46" s="1">
@@ -3730,7 +3748,7 @@
         <v>가정역</v>
       </c>
       <c r="G46" s="2" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>211DOWNMID</v>
       </c>
       <c r="H46" s="1" t="s">
@@ -3740,11 +3758,11 @@
         <v>11</v>
       </c>
       <c r="J46" s="1" t="str">
-        <f>B46&amp;E46</f>
+        <f t="shared" si="0"/>
         <v>211ZONE10</v>
       </c>
       <c r="K46" s="1" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>https://2line.pages.dev/?id=211DOWNMID,211DOWNMID</v>
       </c>
       <c r="L46" s="3" t="s">
@@ -3754,7 +3772,7 @@
     </row>
     <row r="47" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A47" s="1">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>46</v>
       </c>
       <c r="B47" s="1">
@@ -3774,7 +3792,7 @@
         <v>가정역</v>
       </c>
       <c r="G47" s="2" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>211DOWNREAR</v>
       </c>
       <c r="H47" s="1" t="s">
@@ -3784,11 +3802,11 @@
         <v>11</v>
       </c>
       <c r="J47" s="1" t="str">
-        <f>B47&amp;E47</f>
+        <f t="shared" si="0"/>
         <v>211ZONE11</v>
       </c>
       <c r="K47" s="1" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>https://2line.pages.dev/?id=211DOWNREAR,211DOWNREAR</v>
       </c>
       <c r="L47" s="3" t="s">
@@ -3798,7 +3816,7 @@
     </row>
     <row r="48" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A48" s="1">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>47</v>
       </c>
       <c r="B48" s="1">
@@ -3818,7 +3836,7 @@
         <v>가정역</v>
       </c>
       <c r="G48" s="2" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>211STA001</v>
       </c>
       <c r="H48" s="1" t="s">
@@ -3828,11 +3846,11 @@
         <v>11</v>
       </c>
       <c r="J48" s="1" t="str">
-        <f>B48&amp;E48</f>
+        <f t="shared" si="0"/>
         <v>211ZONE02</v>
       </c>
       <c r="K48" s="1" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>https://2line.pages.dev/?id=211STA001,211STA001</v>
       </c>
       <c r="L48" s="3" t="s">
@@ -3842,7 +3860,7 @@
     </row>
     <row r="49" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A49" s="1">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>48</v>
       </c>
       <c r="B49" s="1">
@@ -3862,7 +3880,7 @@
         <v>가정역</v>
       </c>
       <c r="G49" s="2" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>211STA002</v>
       </c>
       <c r="H49" s="1" t="s">
@@ -3872,11 +3890,11 @@
         <v>11</v>
       </c>
       <c r="J49" s="1" t="str">
-        <f>B49&amp;E49</f>
+        <f t="shared" si="0"/>
         <v>211ZONE05</v>
       </c>
       <c r="K49" s="1" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>https://2line.pages.dev/?id=211STA002,211STA002</v>
       </c>
       <c r="L49" s="3" t="s">
@@ -3906,7 +3924,7 @@
         <v>아시아드경기장역</v>
       </c>
       <c r="G50" s="2" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>209ES001</v>
       </c>
       <c r="H50" s="1" t="s">
@@ -3916,11 +3934,11 @@
         <v>275</v>
       </c>
       <c r="J50" s="1" t="str">
-        <f t="shared" ref="J50:J80" si="3">B50&amp;E50</f>
+        <f t="shared" ref="J50:J80" si="4">B50&amp;E50</f>
         <v>209ZONE05</v>
       </c>
       <c r="K50" s="1" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>https://2line.pages.dev/?id=209ES001,209ES001</v>
       </c>
       <c r="L50" s="3" t="s">
@@ -3929,7 +3947,7 @@
     </row>
     <row r="51" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A51" s="1">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>50</v>
       </c>
       <c r="B51" s="1">
@@ -3949,7 +3967,7 @@
         <v>아시아드경기장역</v>
       </c>
       <c r="G51" s="2" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>209ES002</v>
       </c>
       <c r="H51" s="1" t="s">
@@ -3959,11 +3977,11 @@
         <v>275</v>
       </c>
       <c r="J51" s="1" t="str">
+        <f t="shared" si="4"/>
+        <v>209ZONE03</v>
+      </c>
+      <c r="K51" s="1" t="str">
         <f t="shared" si="3"/>
-        <v>209ZONE03</v>
-      </c>
-      <c r="K51" s="1" t="str">
-        <f t="shared" si="2"/>
         <v>https://2line.pages.dev/?id=209ES002,209ES002</v>
       </c>
       <c r="L51" s="3" t="s">
@@ -3972,7 +3990,7 @@
     </row>
     <row r="52" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A52" s="1">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>51</v>
       </c>
       <c r="B52" s="1">
@@ -3992,7 +4010,7 @@
         <v>아시아드경기장역</v>
       </c>
       <c r="G52" s="2" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>209ES003</v>
       </c>
       <c r="H52" s="1" t="s">
@@ -4002,11 +4020,11 @@
         <v>275</v>
       </c>
       <c r="J52" s="1" t="str">
+        <f t="shared" si="4"/>
+        <v>209ZONE07</v>
+      </c>
+      <c r="K52" s="1" t="str">
         <f t="shared" si="3"/>
-        <v>209ZONE07</v>
-      </c>
-      <c r="K52" s="1" t="str">
-        <f t="shared" si="2"/>
         <v>https://2line.pages.dev/?id=209ES003,209ES003</v>
       </c>
       <c r="L52" s="3" t="s">
@@ -4015,7 +4033,7 @@
     </row>
     <row r="53" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A53" s="1">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>52</v>
       </c>
       <c r="B53" s="1">
@@ -4035,7 +4053,7 @@
         <v>아시아드경기장역</v>
       </c>
       <c r="G53" s="2" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>209ES004</v>
       </c>
       <c r="H53" s="1" t="s">
@@ -4045,11 +4063,11 @@
         <v>275</v>
       </c>
       <c r="J53" s="1" t="str">
+        <f t="shared" si="4"/>
+        <v>209ZONE03</v>
+      </c>
+      <c r="K53" s="1" t="str">
         <f t="shared" si="3"/>
-        <v>209ZONE03</v>
-      </c>
-      <c r="K53" s="1" t="str">
-        <f t="shared" si="2"/>
         <v>https://2line.pages.dev/?id=209ES004,209ES004</v>
       </c>
       <c r="L53" s="3" t="s">
@@ -4058,7 +4076,7 @@
     </row>
     <row r="54" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A54" s="1">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>53</v>
       </c>
       <c r="B54" s="1">
@@ -4078,7 +4096,7 @@
         <v>아시아드경기장역</v>
       </c>
       <c r="G54" s="2" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>209ES005</v>
       </c>
       <c r="H54" s="1" t="s">
@@ -4088,11 +4106,11 @@
         <v>275</v>
       </c>
       <c r="J54" s="1" t="str">
+        <f t="shared" si="4"/>
+        <v>209ZONE01</v>
+      </c>
+      <c r="K54" s="1" t="str">
         <f t="shared" si="3"/>
-        <v>209ZONE01</v>
-      </c>
-      <c r="K54" s="1" t="str">
-        <f t="shared" si="2"/>
         <v>https://2line.pages.dev/?id=209ES005,209ES005</v>
       </c>
       <c r="L54" s="3" t="s">
@@ -4101,7 +4119,7 @@
     </row>
     <row r="55" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A55" s="1">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>54</v>
       </c>
       <c r="B55" s="1">
@@ -4121,7 +4139,7 @@
         <v>아시아드경기장역</v>
       </c>
       <c r="G55" s="2" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>209ES006</v>
       </c>
       <c r="H55" s="1" t="s">
@@ -4131,11 +4149,11 @@
         <v>275</v>
       </c>
       <c r="J55" s="1" t="str">
+        <f t="shared" si="4"/>
+        <v>209ZONE01</v>
+      </c>
+      <c r="K55" s="1" t="str">
         <f t="shared" si="3"/>
-        <v>209ZONE01</v>
-      </c>
-      <c r="K55" s="1" t="str">
-        <f t="shared" si="2"/>
         <v>https://2line.pages.dev/?id=209ES006,209ES006</v>
       </c>
       <c r="L55" s="3" t="s">
@@ -4144,7 +4162,7 @@
     </row>
     <row r="56" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A56" s="1">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>55</v>
       </c>
       <c r="B56" s="1">
@@ -4164,7 +4182,7 @@
         <v>아시아드경기장역</v>
       </c>
       <c r="G56" s="2" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>209ES007</v>
       </c>
       <c r="H56" s="1" t="s">
@@ -4174,11 +4192,11 @@
         <v>275</v>
       </c>
       <c r="J56" s="1" t="str">
+        <f t="shared" si="4"/>
+        <v>209ZONE02</v>
+      </c>
+      <c r="K56" s="1" t="str">
         <f t="shared" si="3"/>
-        <v>209ZONE02</v>
-      </c>
-      <c r="K56" s="1" t="str">
-        <f t="shared" si="2"/>
         <v>https://2line.pages.dev/?id=209ES007,209ES007</v>
       </c>
       <c r="L56" s="3" t="s">
@@ -4187,7 +4205,7 @@
     </row>
     <row r="57" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A57" s="1">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>56</v>
       </c>
       <c r="B57" s="1">
@@ -4207,7 +4225,7 @@
         <v>아시아드경기장역</v>
       </c>
       <c r="G57" s="2" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>209ES008</v>
       </c>
       <c r="H57" s="1" t="s">
@@ -4217,11 +4235,11 @@
         <v>275</v>
       </c>
       <c r="J57" s="1" t="str">
+        <f t="shared" si="4"/>
+        <v>209ZONE02</v>
+      </c>
+      <c r="K57" s="1" t="str">
         <f t="shared" si="3"/>
-        <v>209ZONE02</v>
-      </c>
-      <c r="K57" s="1" t="str">
-        <f t="shared" si="2"/>
         <v>https://2line.pages.dev/?id=209ES008,209ES008</v>
       </c>
       <c r="L57" s="3" t="s">
@@ -4230,7 +4248,7 @@
     </row>
     <row r="58" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A58" s="1">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>57</v>
       </c>
       <c r="B58" s="1">
@@ -4250,7 +4268,7 @@
         <v>아시아드경기장역</v>
       </c>
       <c r="G58" s="2" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>209TOILET4M</v>
       </c>
       <c r="H58" s="1" t="s">
@@ -4260,11 +4278,11 @@
         <v>275</v>
       </c>
       <c r="J58" s="1" t="str">
+        <f t="shared" si="4"/>
+        <v>209ZONE03</v>
+      </c>
+      <c r="K58" s="1" t="str">
         <f t="shared" si="3"/>
-        <v>209ZONE03</v>
-      </c>
-      <c r="K58" s="1" t="str">
-        <f t="shared" si="2"/>
         <v>https://2line.pages.dev/?id=209TOILET4M,209TOILET4M</v>
       </c>
       <c r="L58" s="3" t="s">
@@ -4273,7 +4291,7 @@
     </row>
     <row r="59" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A59" s="1">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>58</v>
       </c>
       <c r="B59" s="1">
@@ -4293,7 +4311,7 @@
         <v>아시아드경기장역</v>
       </c>
       <c r="G59" s="2" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>209TOILET4W</v>
       </c>
       <c r="H59" s="1" t="s">
@@ -4303,11 +4321,11 @@
         <v>275</v>
       </c>
       <c r="J59" s="1" t="str">
+        <f t="shared" si="4"/>
+        <v>209ZONE04</v>
+      </c>
+      <c r="K59" s="1" t="str">
         <f t="shared" si="3"/>
-        <v>209ZONE04</v>
-      </c>
-      <c r="K59" s="1" t="str">
-        <f t="shared" si="2"/>
         <v>https://2line.pages.dev/?id=209TOILET4W,209TOILET4W</v>
       </c>
       <c r="L59" s="3" t="s">
@@ -4316,7 +4334,7 @@
     </row>
     <row r="60" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A60" s="1">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>59</v>
       </c>
       <c r="B60" s="1">
@@ -4336,7 +4354,7 @@
         <v>아시아드경기장역</v>
       </c>
       <c r="G60" s="2" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>209EL001</v>
       </c>
       <c r="H60" s="1" t="s">
@@ -4346,11 +4364,11 @@
         <v>275</v>
       </c>
       <c r="J60" s="1" t="str">
+        <f t="shared" si="4"/>
+        <v>209ZONE04</v>
+      </c>
+      <c r="K60" s="1" t="str">
         <f t="shared" si="3"/>
-        <v>209ZONE04</v>
-      </c>
-      <c r="K60" s="1" t="str">
-        <f t="shared" si="2"/>
         <v>https://2line.pages.dev/?id=209EL001,209EL001</v>
       </c>
       <c r="L60" s="3" t="s">
@@ -4359,7 +4377,7 @@
     </row>
     <row r="61" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A61" s="1">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>60</v>
       </c>
       <c r="B61" s="1">
@@ -4379,7 +4397,7 @@
         <v>아시아드경기장역</v>
       </c>
       <c r="G61" s="2" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>209EL002</v>
       </c>
       <c r="H61" s="1" t="s">
@@ -4389,11 +4407,11 @@
         <v>275</v>
       </c>
       <c r="J61" s="1" t="str">
+        <f t="shared" si="4"/>
+        <v>209ZONE06</v>
+      </c>
+      <c r="K61" s="1" t="str">
         <f t="shared" si="3"/>
-        <v>209ZONE06</v>
-      </c>
-      <c r="K61" s="1" t="str">
-        <f t="shared" si="2"/>
         <v>https://2line.pages.dev/?id=209EL002,209EL002</v>
       </c>
       <c r="L61" s="3" t="s">
@@ -4402,7 +4420,7 @@
     </row>
     <row r="62" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A62" s="1">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>61</v>
       </c>
       <c r="B62" s="1">
@@ -4422,7 +4440,7 @@
         <v>아시아드경기장역</v>
       </c>
       <c r="G62" s="2" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>209EL003</v>
       </c>
       <c r="H62" s="1" t="s">
@@ -4432,11 +4450,11 @@
         <v>275</v>
       </c>
       <c r="J62" s="1" t="str">
+        <f t="shared" si="4"/>
+        <v>209ZONE01</v>
+      </c>
+      <c r="K62" s="1" t="str">
         <f t="shared" si="3"/>
-        <v>209ZONE01</v>
-      </c>
-      <c r="K62" s="1" t="str">
-        <f t="shared" si="2"/>
         <v>https://2line.pages.dev/?id=209EL003,209EL003</v>
       </c>
       <c r="L62" s="3" t="s">
@@ -4445,7 +4463,7 @@
     </row>
     <row r="63" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A63" s="1">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>62</v>
       </c>
       <c r="B63" s="1">
@@ -4465,7 +4483,7 @@
         <v>아시아드경기장역</v>
       </c>
       <c r="G63" s="2" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>209EL004</v>
       </c>
       <c r="H63" s="1" t="s">
@@ -4475,11 +4493,11 @@
         <v>275</v>
       </c>
       <c r="J63" s="1" t="str">
+        <f t="shared" si="4"/>
+        <v>209ZONE02</v>
+      </c>
+      <c r="K63" s="1" t="str">
         <f t="shared" si="3"/>
-        <v>209ZONE02</v>
-      </c>
-      <c r="K63" s="1" t="str">
-        <f t="shared" si="2"/>
         <v>https://2line.pages.dev/?id=209EL004,209EL004</v>
       </c>
       <c r="L63" s="3" t="s">
@@ -4488,7 +4506,7 @@
     </row>
     <row r="64" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A64" s="1">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>63</v>
       </c>
       <c r="B64" s="1">
@@ -4508,7 +4526,7 @@
         <v>아시아드경기장역</v>
       </c>
       <c r="G64" s="2" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>209EXIT001</v>
       </c>
       <c r="H64" s="1" t="s">
@@ -4518,11 +4536,11 @@
         <v>275</v>
       </c>
       <c r="J64" s="1" t="str">
+        <f t="shared" si="4"/>
+        <v>209ZONE01</v>
+      </c>
+      <c r="K64" s="1" t="str">
         <f t="shared" si="3"/>
-        <v>209ZONE01</v>
-      </c>
-      <c r="K64" s="1" t="str">
-        <f t="shared" si="2"/>
         <v>https://2line.pages.dev/?id=209EXIT001,209EXIT001</v>
       </c>
       <c r="L64" s="3" t="s">
@@ -4531,7 +4549,7 @@
     </row>
     <row r="65" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A65" s="1">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>64</v>
       </c>
       <c r="B65" s="1">
@@ -4551,7 +4569,7 @@
         <v>아시아드경기장역</v>
       </c>
       <c r="G65" s="2" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>209EXIT002</v>
       </c>
       <c r="H65" s="1" t="s">
@@ -4561,11 +4579,11 @@
         <v>275</v>
       </c>
       <c r="J65" s="1" t="str">
+        <f t="shared" si="4"/>
+        <v>209ZONE01</v>
+      </c>
+      <c r="K65" s="1" t="str">
         <f t="shared" si="3"/>
-        <v>209ZONE01</v>
-      </c>
-      <c r="K65" s="1" t="str">
-        <f t="shared" si="2"/>
         <v>https://2line.pages.dev/?id=209EXIT002,209EXIT002</v>
       </c>
       <c r="L65" s="3" t="s">
@@ -4574,7 +4592,7 @@
     </row>
     <row r="66" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A66" s="1">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>65</v>
       </c>
       <c r="B66" s="1">
@@ -4594,7 +4612,7 @@
         <v>아시아드경기장역</v>
       </c>
       <c r="G66" s="2" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>209EXIT003</v>
       </c>
       <c r="H66" s="1" t="s">
@@ -4604,11 +4622,11 @@
         <v>275</v>
       </c>
       <c r="J66" s="1" t="str">
+        <f t="shared" si="4"/>
+        <v>209ZONE02</v>
+      </c>
+      <c r="K66" s="1" t="str">
         <f t="shared" si="3"/>
-        <v>209ZONE02</v>
-      </c>
-      <c r="K66" s="1" t="str">
-        <f t="shared" si="2"/>
         <v>https://2line.pages.dev/?id=209EXIT003,209EXIT003</v>
       </c>
       <c r="L66" s="3" t="s">
@@ -4617,7 +4635,7 @@
     </row>
     <row r="67" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A67" s="1">
-        <f t="shared" ref="A67:A82" si="4">ROW()-1</f>
+        <f t="shared" ref="A67:A82" si="5">ROW()-1</f>
         <v>66</v>
       </c>
       <c r="B67" s="1">
@@ -4637,7 +4655,7 @@
         <v>아시아드경기장역</v>
       </c>
       <c r="G67" s="2" t="str">
-        <f t="shared" ref="G67:G80" si="5">B67&amp;C67&amp;TEXT(D67,"000")</f>
+        <f t="shared" ref="G67:G80" si="6">B67&amp;C67&amp;TEXT(D67,"000")</f>
         <v>209EXIT004</v>
       </c>
       <c r="H67" s="1" t="s">
@@ -4647,11 +4665,11 @@
         <v>275</v>
       </c>
       <c r="J67" s="1" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>209ZONE02</v>
       </c>
       <c r="K67" s="1" t="str">
-        <f t="shared" ref="K67:L80" si="6">"https://2line.pages.dev/?id="&amp;G67&amp;","&amp;G67</f>
+        <f t="shared" ref="K67:K80" si="7">"https://2line.pages.dev/?id="&amp;G67&amp;","&amp;G67</f>
         <v>https://2line.pages.dev/?id=209EXIT004,209EXIT004</v>
       </c>
       <c r="L67" s="3" t="s">
@@ -4660,7 +4678,7 @@
     </row>
     <row r="68" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A68" s="1">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>67</v>
       </c>
       <c r="B68" s="1">
@@ -4680,7 +4698,7 @@
         <v>가정중앙시장역</v>
       </c>
       <c r="G68" s="2" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>212ES001</v>
       </c>
       <c r="H68" s="1" t="s">
@@ -4690,11 +4708,11 @@
         <v>322</v>
       </c>
       <c r="J68" s="1" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>212ZONE05</v>
       </c>
       <c r="K68" s="1" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>https://2line.pages.dev/?id=212ES001,212ES001</v>
       </c>
       <c r="L68" s="3" t="s">
@@ -4703,7 +4721,7 @@
     </row>
     <row r="69" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A69" s="1">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>68</v>
       </c>
       <c r="B69" s="1">
@@ -4723,7 +4741,7 @@
         <v>가정중앙시장역</v>
       </c>
       <c r="G69" s="2" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>212ES002</v>
       </c>
       <c r="H69" s="1" t="s">
@@ -4733,11 +4751,11 @@
         <v>322</v>
       </c>
       <c r="J69" s="1" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>212ZONE03</v>
       </c>
       <c r="K69" s="1" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>https://2line.pages.dev/?id=212ES002,212ES002</v>
       </c>
       <c r="L69" s="3" t="s">
@@ -4746,7 +4764,7 @@
     </row>
     <row r="70" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A70" s="1">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>69</v>
       </c>
       <c r="B70" s="1">
@@ -4766,7 +4784,7 @@
         <v>가정중앙시장역</v>
       </c>
       <c r="G70" s="2" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>212ES003</v>
       </c>
       <c r="H70" s="1" t="s">
@@ -4776,11 +4794,11 @@
         <v>322</v>
       </c>
       <c r="J70" s="1" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>212ZONE07</v>
       </c>
       <c r="K70" s="1" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>https://2line.pages.dev/?id=212ES003,212ES003</v>
       </c>
       <c r="L70" s="3" t="s">
@@ -4789,7 +4807,7 @@
     </row>
     <row r="71" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A71" s="1">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>70</v>
       </c>
       <c r="B71" s="1">
@@ -4809,7 +4827,7 @@
         <v>가정중앙시장역</v>
       </c>
       <c r="G71" s="2" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>212ES004</v>
       </c>
       <c r="H71" s="1" t="s">
@@ -4819,11 +4837,11 @@
         <v>322</v>
       </c>
       <c r="J71" s="1" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>212ZONE03</v>
       </c>
       <c r="K71" s="1" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>https://2line.pages.dev/?id=212ES004,212ES004</v>
       </c>
       <c r="L71" s="3" t="s">
@@ -4832,7 +4850,7 @@
     </row>
     <row r="72" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A72" s="1">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>71</v>
       </c>
       <c r="B72" s="1">
@@ -4852,7 +4870,7 @@
         <v>가정중앙시장역</v>
       </c>
       <c r="G72" s="2" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>212ES005</v>
       </c>
       <c r="H72" s="1" t="s">
@@ -4862,11 +4880,11 @@
         <v>322</v>
       </c>
       <c r="J72" s="1" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>212ZONE01</v>
       </c>
       <c r="K72" s="1" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>https://2line.pages.dev/?id=212ES005,212ES005</v>
       </c>
       <c r="L72" s="3" t="s">
@@ -4875,7 +4893,7 @@
     </row>
     <row r="73" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A73" s="1">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>72</v>
       </c>
       <c r="B73" s="1">
@@ -4895,7 +4913,7 @@
         <v>가정중앙시장역</v>
       </c>
       <c r="G73" s="2" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>212ES006</v>
       </c>
       <c r="H73" s="1" t="s">
@@ -4905,11 +4923,11 @@
         <v>322</v>
       </c>
       <c r="J73" s="1" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>212ZONE01</v>
       </c>
       <c r="K73" s="1" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>https://2line.pages.dev/?id=212ES006,212ES006</v>
       </c>
       <c r="L73" s="3" t="s">
@@ -4918,7 +4936,7 @@
     </row>
     <row r="74" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A74" s="1">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>73</v>
       </c>
       <c r="B74" s="1">
@@ -4938,7 +4956,7 @@
         <v>가정중앙시장역</v>
       </c>
       <c r="G74" s="2" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>212EL001</v>
       </c>
       <c r="H74" s="1" t="s">
@@ -4948,11 +4966,11 @@
         <v>322</v>
       </c>
       <c r="J74" s="1" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>212ZONE04</v>
       </c>
       <c r="K74" s="1" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>https://2line.pages.dev/?id=212EL001,212EL001</v>
       </c>
       <c r="L74" s="3" t="s">
@@ -4961,7 +4979,7 @@
     </row>
     <row r="75" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A75" s="1">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>74</v>
       </c>
       <c r="B75" s="1">
@@ -4981,7 +4999,7 @@
         <v>가정중앙시장역</v>
       </c>
       <c r="G75" s="2" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>212EL002</v>
       </c>
       <c r="H75" s="1" t="s">
@@ -4991,11 +5009,11 @@
         <v>322</v>
       </c>
       <c r="J75" s="1" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>212ZONE06</v>
       </c>
       <c r="K75" s="1" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>https://2line.pages.dev/?id=212EL002,212EL002</v>
       </c>
       <c r="L75" s="3" t="s">
@@ -5004,7 +5022,7 @@
     </row>
     <row r="76" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A76" s="1">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>75</v>
       </c>
       <c r="B76" s="1">
@@ -5024,7 +5042,7 @@
         <v>가정중앙시장역</v>
       </c>
       <c r="G76" s="2" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>212EL003</v>
       </c>
       <c r="H76" s="1" t="s">
@@ -5034,11 +5052,11 @@
         <v>322</v>
       </c>
       <c r="J76" s="1" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>212ZONE01</v>
       </c>
       <c r="K76" s="1" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>https://2line.pages.dev/?id=212EL003,212EL003</v>
       </c>
       <c r="L76" s="3" t="s">
@@ -5047,7 +5065,7 @@
     </row>
     <row r="77" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A77" s="1">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>76</v>
       </c>
       <c r="B77" s="1">
@@ -5067,7 +5085,7 @@
         <v>가정중앙시장역</v>
       </c>
       <c r="G77" s="2" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>212EL004</v>
       </c>
       <c r="H77" s="1" t="s">
@@ -5077,11 +5095,11 @@
         <v>322</v>
       </c>
       <c r="J77" s="1" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>212ZONE02</v>
       </c>
       <c r="K77" s="1" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>https://2line.pages.dev/?id=212EL004,212EL004</v>
       </c>
       <c r="L77" s="3" t="s">
@@ -5090,7 +5108,7 @@
     </row>
     <row r="78" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A78" s="1">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>77</v>
       </c>
       <c r="B78" s="1">
@@ -5110,7 +5128,7 @@
         <v>가정중앙시장역</v>
       </c>
       <c r="G78" s="2" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>212EL005</v>
       </c>
       <c r="H78" s="1" t="s">
@@ -5120,11 +5138,11 @@
         <v>322</v>
       </c>
       <c r="J78" s="1" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>212ZONE02</v>
       </c>
       <c r="K78" s="1" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>https://2line.pages.dev/?id=212EL005,212EL005</v>
       </c>
       <c r="L78" s="3" t="s">
@@ -5133,7 +5151,7 @@
     </row>
     <row r="79" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A79" s="1">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>78</v>
       </c>
       <c r="B79" s="1">
@@ -5153,7 +5171,7 @@
         <v>가정중앙시장역</v>
       </c>
       <c r="G79" s="2" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>212TOILET1M</v>
       </c>
       <c r="H79" s="1" t="s">
@@ -5163,11 +5181,11 @@
         <v>322</v>
       </c>
       <c r="J79" s="1" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>212ZONE01</v>
       </c>
       <c r="K79" s="1" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>https://2line.pages.dev/?id=212TOILET1M,212TOILET1M</v>
       </c>
       <c r="L79" s="3" t="s">
@@ -5176,7 +5194,7 @@
     </row>
     <row r="80" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A80" s="1">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>79</v>
       </c>
       <c r="B80" s="1">
@@ -5196,7 +5214,7 @@
         <v>가정중앙시장역</v>
       </c>
       <c r="G80" s="2" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>212TOILET1W</v>
       </c>
       <c r="H80" s="1" t="s">
@@ -5206,11 +5224,11 @@
         <v>322</v>
       </c>
       <c r="J80" s="1" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>212ZONE01</v>
       </c>
       <c r="K80" s="1" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>https://2line.pages.dev/?id=212TOILET1W,212TOILET1W</v>
       </c>
       <c r="L80" s="3" t="s">
@@ -5219,7 +5237,7 @@
     </row>
     <row r="81" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A81" s="1">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>80</v>
       </c>
       <c r="B81" s="1">
@@ -5239,7 +5257,7 @@
         <v>가정중앙시장역</v>
       </c>
       <c r="G81" s="2" t="str">
-        <f t="shared" ref="G81:G82" si="7">B81&amp;C81&amp;TEXT(D81,"000")</f>
+        <f t="shared" ref="G81:G83" si="8">B81&amp;C81&amp;TEXT(D81,"000")</f>
         <v>212EXIT001</v>
       </c>
       <c r="H81" s="1" t="s">
@@ -5249,11 +5267,11 @@
         <v>322</v>
       </c>
       <c r="J81" s="1" t="str">
-        <f t="shared" ref="J81:J82" si="8">B81&amp;E81</f>
+        <f t="shared" ref="J81:J82" si="9">B81&amp;E81</f>
         <v>212ZONE01</v>
       </c>
       <c r="K81" s="1" t="str">
-        <f t="shared" ref="K81:L82" si="9">"https://2line.pages.dev/?id="&amp;G81&amp;","&amp;G81</f>
+        <f t="shared" ref="K81:K83" si="10">"https://2line.pages.dev/?id="&amp;G81&amp;","&amp;G81</f>
         <v>https://2line.pages.dev/?id=212EXIT001,212EXIT001</v>
       </c>
       <c r="L81" s="3" t="s">
@@ -5262,7 +5280,7 @@
     </row>
     <row r="82" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A82" s="1">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>81</v>
       </c>
       <c r="B82" s="1">
@@ -5282,7 +5300,7 @@
         <v>가정중앙시장역</v>
       </c>
       <c r="G82" s="2" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>212EXIT002</v>
       </c>
       <c r="H82" s="1" t="s">
@@ -5292,15 +5310,195 @@
         <v>322</v>
       </c>
       <c r="J82" s="1" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>212ZONE01</v>
       </c>
       <c r="K82" s="1" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>https://2line.pages.dev/?id=212EXIT002,212EXIT002</v>
       </c>
       <c r="L82" s="3" t="s">
         <v>355</v>
+      </c>
+    </row>
+    <row r="83" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="B83" s="1">
+        <v>210</v>
+      </c>
+      <c r="C83" s="1" t="s">
+        <v>279</v>
+      </c>
+      <c r="D83" s="2">
+        <v>1</v>
+      </c>
+      <c r="E83" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="F83" s="1" t="str">
+        <f>VLOOKUP(B83,Sheet2!$G$2:$H$28,2,FALSE)</f>
+        <v>서해구청역</v>
+      </c>
+      <c r="G83" s="2" t="str">
+        <f t="shared" ref="G83:G87" si="11">B83&amp;C83&amp;TEXT(D83,"000")</f>
+        <v>210EXIT001</v>
+      </c>
+      <c r="H83" s="1" t="s">
+        <v>374</v>
+      </c>
+      <c r="I83" s="1" t="s">
+        <v>377</v>
+      </c>
+      <c r="J83" s="1" t="str">
+        <f t="shared" ref="J83:J87" si="12">B83&amp;E83</f>
+        <v>210ZONE01</v>
+      </c>
+      <c r="K83" s="1" t="str">
+        <f t="shared" ref="K83:K87" si="13">"https://2line.pages.dev/?id="&amp;G83&amp;","&amp;G83</f>
+        <v>https://2line.pages.dev/?id=210EXIT001,210EXIT001</v>
+      </c>
+    </row>
+    <row r="84" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="B84" s="1">
+        <v>210</v>
+      </c>
+      <c r="C84" s="1" t="s">
+        <v>279</v>
+      </c>
+      <c r="D84" s="2">
+        <v>2</v>
+      </c>
+      <c r="E84" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="F84" s="1" t="str">
+        <f>VLOOKUP(B84,Sheet2!$G$2:$H$28,2,FALSE)</f>
+        <v>서해구청역</v>
+      </c>
+      <c r="G84" s="2" t="str">
+        <f t="shared" si="11"/>
+        <v>210EXIT002</v>
+      </c>
+      <c r="H84" s="1" t="s">
+        <v>375</v>
+      </c>
+      <c r="I84" s="1" t="s">
+        <v>377</v>
+      </c>
+      <c r="J84" s="1" t="str">
+        <f t="shared" si="12"/>
+        <v>210ZONE01</v>
+      </c>
+      <c r="K84" s="1" t="str">
+        <f t="shared" si="13"/>
+        <v>https://2line.pages.dev/?id=210EXIT002,210EXIT002</v>
+      </c>
+    </row>
+    <row r="85" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="B85" s="1">
+        <v>210</v>
+      </c>
+      <c r="C85" s="1" t="s">
+        <v>279</v>
+      </c>
+      <c r="D85" s="2">
+        <v>3</v>
+      </c>
+      <c r="E85" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="F85" s="1" t="str">
+        <f>VLOOKUP(B85,Sheet2!$G$2:$H$28,2,FALSE)</f>
+        <v>서해구청역</v>
+      </c>
+      <c r="G85" s="2" t="str">
+        <f t="shared" si="11"/>
+        <v>210EXIT003</v>
+      </c>
+      <c r="H85" s="1" t="s">
+        <v>372</v>
+      </c>
+      <c r="I85" s="1" t="s">
+        <v>377</v>
+      </c>
+      <c r="J85" s="1" t="str">
+        <f t="shared" si="12"/>
+        <v>210ZONE02</v>
+      </c>
+      <c r="K85" s="1" t="str">
+        <f t="shared" si="13"/>
+        <v>https://2line.pages.dev/?id=210EXIT003,210EXIT003</v>
+      </c>
+    </row>
+    <row r="86" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="B86" s="1">
+        <v>210</v>
+      </c>
+      <c r="C86" s="1" t="s">
+        <v>279</v>
+      </c>
+      <c r="D86" s="2">
+        <v>4</v>
+      </c>
+      <c r="E86" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="F86" s="1" t="str">
+        <f>VLOOKUP(B86,Sheet2!$G$2:$H$28,2,FALSE)</f>
+        <v>서해구청역</v>
+      </c>
+      <c r="G86" s="2" t="str">
+        <f t="shared" si="11"/>
+        <v>210EXIT004</v>
+      </c>
+      <c r="H86" s="1" t="s">
+        <v>373</v>
+      </c>
+      <c r="I86" s="1" t="s">
+        <v>377</v>
+      </c>
+      <c r="J86" s="1" t="str">
+        <f t="shared" si="12"/>
+        <v>210ZONE03</v>
+      </c>
+      <c r="K86" s="1" t="str">
+        <f t="shared" si="13"/>
+        <v>https://2line.pages.dev/?id=210EXIT004,210EXIT004</v>
+      </c>
+    </row>
+    <row r="87" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="B87" s="1">
+        <v>210</v>
+      </c>
+      <c r="C87" s="1" t="s">
+        <v>277</v>
+      </c>
+      <c r="D87" s="2">
+        <v>1</v>
+      </c>
+      <c r="E87" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="F87" s="1" t="str">
+        <f>VLOOKUP(B87,Sheet2!$G$2:$H$28,2,FALSE)</f>
+        <v>서해구청역</v>
+      </c>
+      <c r="G87" s="2" t="str">
+        <f t="shared" si="11"/>
+        <v>210TOILET001</v>
+      </c>
+      <c r="H87" s="1" t="s">
+        <v>376</v>
+      </c>
+      <c r="I87" s="1" t="s">
+        <v>377</v>
+      </c>
+      <c r="J87" s="1" t="str">
+        <f t="shared" si="12"/>
+        <v>210ZONE03</v>
+      </c>
+      <c r="K87" s="1" t="str">
+        <f t="shared" si="13"/>
+        <v>https://2line.pages.dev/?id=210TOILET001,210TOILET001</v>
       </c>
     </row>
   </sheetData>
@@ -5423,10 +5621,10 @@
       <c r="E1" s="1" t="s">
         <v>180</v>
       </c>
-      <c r="G1" s="5" t="s">
+      <c r="G1" s="7" t="s">
         <v>225</v>
       </c>
-      <c r="H1" s="5"/>
+      <c r="H1" s="7"/>
     </row>
     <row r="2" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A2" s="1" t="s">

--- a/data.xlsx
+++ b/data.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30131"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="24334"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Musicat\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\박경태\python\2Line2-main\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EFA2E1F1-DF39-4E71-BB78-A7ED2E0C10C8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A79FE10D-38E8-464A-8AB6-E16C97CAF8B6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-105" yWindow="0" windowWidth="14610" windowHeight="15585" xr2:uid="{21F0DF5A-062E-4FED-9C31-648F525201B8}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{21F0DF5A-062E-4FED-9C31-648F525201B8}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -30,12 +30,15 @@
         <xcalcf:feature name="microsoft.com:LET_WF"/>
       </xcalcf:calcFeatures>
     </ext>
+    <ext xmlns:xlwcv="http://schemas.microsoft.com/office/spreadsheetml/2024/workbookCompatibilityVersion" uri="{D14903EA-33C4-47F7-8F05-3474C54BE107}">
+      <xlwcv:version setVersion="1"/>
+    </ext>
   </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="889" uniqueCount="378">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="964" uniqueCount="402">
   <si>
     <t>연번</t>
     <phoneticPr fontId="2" type="noConversion"/>
@@ -1326,6 +1329,99 @@
   </si>
   <si>
     <t>032-451-4310</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>에스컬레이터 1호기</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>엘리베이터 1호기</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>엘리베이터 2호기</t>
+  </si>
+  <si>
+    <t>엘리베이터 3호기</t>
+  </si>
+  <si>
+    <t>엘리베이터 4호기</t>
+  </si>
+  <si>
+    <t>https://2line.pages.dev/?id=210EXIT001</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>https://2line.pages.dev/?id=210EXIT002</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>https://2line.pages.dev/?id=210EXIT003</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>https://2line.pages.dev/?id=210EXIT004</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>https://2line.pages.dev/?id=210TOILET001</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>https://2line.pages.dev/?id=210ES001</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>https://2line.pages.dev/?id=210ES002</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>https://2line.pages.dev/?id=210ES003</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>https://2line.pages.dev/?id=210ES004</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>https://2line.pages.dev/?id=210ES005</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>https://2line.pages.dev/?id=210ES006</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>https://2line.pages.dev/?id=210ES007</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>https://2line.pages.dev/?id=210ES008</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>https://2line.pages.dev/?id=210ES009</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>https://2line.pages.dev/?id=210ES010</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>https://2line.pages.dev/?id=210EL001</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>https://2line.pages.dev/?id=210EL002</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>https://2line.pages.dev/?id=210EL003</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>https://2line.pages.dev/?id=210EL004</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
 </sst>
@@ -1393,7 +1489,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="9">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -1418,6 +1514,9 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="표준" xfId="0" builtinId="0"/>
@@ -1437,9 +1536,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 2013 - 2022 테마">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 테마">
   <a:themeElements>
-    <a:clrScheme name="Office 2013 - 2022">
+    <a:clrScheme name="Office">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -1477,7 +1576,7 @@
         <a:srgbClr val="954F72"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office 2013 - 2022">
+    <a:fontScheme name="Office">
       <a:majorFont>
         <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
@@ -1583,7 +1682,7 @@
         <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office 2013 - 2022">
+    <a:fmtScheme name="Office">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -1725,7 +1824,7 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office 2013 - 2022 Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
@@ -1733,7 +1832,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{98156557-3AEA-41A3-9863-FC7FAA63B0F4}">
-  <dimension ref="A1:X87"/>
+  <dimension ref="A1:X101"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="5.25" style="1" bestFit="1" customWidth="1"/>
@@ -4635,7 +4734,7 @@
     </row>
     <row r="67" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A67" s="1">
-        <f t="shared" ref="A67:A82" si="5">ROW()-1</f>
+        <f t="shared" ref="A67:A101" si="5">ROW()-1</f>
         <v>66</v>
       </c>
       <c r="B67" s="1">
@@ -5257,7 +5356,7 @@
         <v>가정중앙시장역</v>
       </c>
       <c r="G81" s="2" t="str">
-        <f t="shared" ref="G81:G83" si="8">B81&amp;C81&amp;TEXT(D81,"000")</f>
+        <f t="shared" ref="G81:G82" si="8">B81&amp;C81&amp;TEXT(D81,"000")</f>
         <v>212EXIT001</v>
       </c>
       <c r="H81" s="1" t="s">
@@ -5271,7 +5370,7 @@
         <v>212ZONE01</v>
       </c>
       <c r="K81" s="1" t="str">
-        <f t="shared" ref="K81:K83" si="10">"https://2line.pages.dev/?id="&amp;G81&amp;","&amp;G81</f>
+        <f t="shared" ref="K81:K82" si="10">"https://2line.pages.dev/?id="&amp;G81&amp;","&amp;G81</f>
         <v>https://2line.pages.dev/?id=212EXIT001,212EXIT001</v>
       </c>
       <c r="L81" s="3" t="s">
@@ -5322,6 +5421,10 @@
       </c>
     </row>
     <row r="83" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A83" s="7">
+        <f t="shared" si="5"/>
+        <v>82</v>
+      </c>
       <c r="B83" s="1">
         <v>210</v>
       </c>
@@ -5353,11 +5456,18 @@
         <v>210ZONE01</v>
       </c>
       <c r="K83" s="1" t="str">
-        <f t="shared" ref="K83:K87" si="13">"https://2line.pages.dev/?id="&amp;G83&amp;","&amp;G83</f>
+        <f t="shared" ref="K83:L88" si="13">"https://2line.pages.dev/?id="&amp;G83&amp;","&amp;G83</f>
         <v>https://2line.pages.dev/?id=210EXIT001,210EXIT001</v>
       </c>
+      <c r="L83" s="3" t="s">
+        <v>383</v>
+      </c>
     </row>
     <row r="84" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A84" s="7">
+        <f t="shared" si="5"/>
+        <v>83</v>
+      </c>
       <c r="B84" s="1">
         <v>210</v>
       </c>
@@ -5392,8 +5502,15 @@
         <f t="shared" si="13"/>
         <v>https://2line.pages.dev/?id=210EXIT002,210EXIT002</v>
       </c>
+      <c r="L84" s="3" t="s">
+        <v>384</v>
+      </c>
     </row>
     <row r="85" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A85" s="7">
+        <f t="shared" si="5"/>
+        <v>84</v>
+      </c>
       <c r="B85" s="1">
         <v>210</v>
       </c>
@@ -5428,8 +5545,15 @@
         <f t="shared" si="13"/>
         <v>https://2line.pages.dev/?id=210EXIT003,210EXIT003</v>
       </c>
+      <c r="L85" s="3" t="s">
+        <v>385</v>
+      </c>
     </row>
     <row r="86" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A86" s="7">
+        <f t="shared" si="5"/>
+        <v>85</v>
+      </c>
       <c r="B86" s="1">
         <v>210</v>
       </c>
@@ -5464,8 +5588,15 @@
         <f t="shared" si="13"/>
         <v>https://2line.pages.dev/?id=210EXIT004,210EXIT004</v>
       </c>
+      <c r="L86" s="3" t="s">
+        <v>386</v>
+      </c>
     </row>
     <row r="87" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A87" s="7">
+        <f t="shared" si="5"/>
+        <v>86</v>
+      </c>
       <c r="B87" s="1">
         <v>210</v>
       </c>
@@ -5499,6 +5630,611 @@
       <c r="K87" s="1" t="str">
         <f t="shared" si="13"/>
         <v>https://2line.pages.dev/?id=210TOILET001,210TOILET001</v>
+      </c>
+      <c r="L87" s="3" t="s">
+        <v>387</v>
+      </c>
+    </row>
+    <row r="88" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A88" s="7">
+        <f t="shared" si="5"/>
+        <v>87</v>
+      </c>
+      <c r="B88" s="7">
+        <v>210</v>
+      </c>
+      <c r="C88" s="1" t="s">
+        <v>276</v>
+      </c>
+      <c r="D88" s="2">
+        <v>1</v>
+      </c>
+      <c r="E88" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="F88" s="7" t="str">
+        <f>VLOOKUP(B88,Sheet2!$G$2:$H$28,2,FALSE)</f>
+        <v>서해구청역</v>
+      </c>
+      <c r="G88" s="2" t="str">
+        <f t="shared" ref="G88:G101" si="14">B88&amp;C88&amp;TEXT(D88,"000")</f>
+        <v>210ES001</v>
+      </c>
+      <c r="H88" s="7" t="s">
+        <v>378</v>
+      </c>
+      <c r="I88" s="7" t="s">
+        <v>377</v>
+      </c>
+      <c r="J88" s="7" t="str">
+        <f t="shared" ref="J88:J101" si="15">B88&amp;E88</f>
+        <v>210ZONE06</v>
+      </c>
+      <c r="K88" s="7" t="str">
+        <f t="shared" ref="K88:L102" si="16">"https://2line.pages.dev/?id="&amp;G88&amp;","&amp;G88</f>
+        <v>https://2line.pages.dev/?id=210ES001,210ES001</v>
+      </c>
+      <c r="L88" s="3" t="s">
+        <v>388</v>
+      </c>
+    </row>
+    <row r="89" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A89" s="7">
+        <f t="shared" si="5"/>
+        <v>88</v>
+      </c>
+      <c r="B89" s="7">
+        <v>210</v>
+      </c>
+      <c r="C89" s="7" t="s">
+        <v>276</v>
+      </c>
+      <c r="D89" s="2">
+        <v>2</v>
+      </c>
+      <c r="E89" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="F89" s="7" t="str">
+        <f>VLOOKUP(B89,Sheet2!$G$2:$H$28,2,FALSE)</f>
+        <v>서해구청역</v>
+      </c>
+      <c r="G89" s="2" t="str">
+        <f t="shared" si="14"/>
+        <v>210ES002</v>
+      </c>
+      <c r="H89" s="7" t="s">
+        <v>130</v>
+      </c>
+      <c r="I89" s="7" t="s">
+        <v>377</v>
+      </c>
+      <c r="J89" s="7" t="str">
+        <f t="shared" si="15"/>
+        <v>210ZONE07</v>
+      </c>
+      <c r="K89" s="7" t="str">
+        <f t="shared" si="16"/>
+        <v>https://2line.pages.dev/?id=210ES002,210ES002</v>
+      </c>
+      <c r="L89" s="3" t="s">
+        <v>389</v>
+      </c>
+    </row>
+    <row r="90" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A90" s="7">
+        <f t="shared" si="5"/>
+        <v>89</v>
+      </c>
+      <c r="B90" s="7">
+        <v>210</v>
+      </c>
+      <c r="C90" s="7" t="s">
+        <v>276</v>
+      </c>
+      <c r="D90" s="2">
+        <v>3</v>
+      </c>
+      <c r="E90" s="7" t="s">
+        <v>24</v>
+      </c>
+      <c r="F90" s="7" t="str">
+        <f>VLOOKUP(B90,Sheet2!$G$2:$H$28,2,FALSE)</f>
+        <v>서해구청역</v>
+      </c>
+      <c r="G90" s="2" t="str">
+        <f t="shared" si="14"/>
+        <v>210ES003</v>
+      </c>
+      <c r="H90" s="7" t="s">
+        <v>131</v>
+      </c>
+      <c r="I90" s="7" t="s">
+        <v>377</v>
+      </c>
+      <c r="J90" s="7" t="str">
+        <f t="shared" si="15"/>
+        <v>210ZONE06</v>
+      </c>
+      <c r="K90" s="7" t="str">
+        <f t="shared" si="16"/>
+        <v>https://2line.pages.dev/?id=210ES003,210ES003</v>
+      </c>
+      <c r="L90" s="3" t="s">
+        <v>390</v>
+      </c>
+    </row>
+    <row r="91" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A91" s="7">
+        <f t="shared" si="5"/>
+        <v>90</v>
+      </c>
+      <c r="B91" s="7">
+        <v>210</v>
+      </c>
+      <c r="C91" s="7" t="s">
+        <v>276</v>
+      </c>
+      <c r="D91" s="2">
+        <v>4</v>
+      </c>
+      <c r="E91" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="F91" s="7" t="str">
+        <f>VLOOKUP(B91,Sheet2!$G$2:$H$28,2,FALSE)</f>
+        <v>서해구청역</v>
+      </c>
+      <c r="G91" s="2" t="str">
+        <f t="shared" si="14"/>
+        <v>210ES004</v>
+      </c>
+      <c r="H91" s="7" t="s">
+        <v>132</v>
+      </c>
+      <c r="I91" s="7" t="s">
+        <v>377</v>
+      </c>
+      <c r="J91" s="7" t="str">
+        <f t="shared" si="15"/>
+        <v>210ZONE08</v>
+      </c>
+      <c r="K91" s="7" t="str">
+        <f t="shared" si="16"/>
+        <v>https://2line.pages.dev/?id=210ES004,210ES004</v>
+      </c>
+      <c r="L91" s="3" t="s">
+        <v>391</v>
+      </c>
+    </row>
+    <row r="92" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A92" s="7">
+        <f t="shared" si="5"/>
+        <v>91</v>
+      </c>
+      <c r="B92" s="7">
+        <v>210</v>
+      </c>
+      <c r="C92" s="7" t="s">
+        <v>276</v>
+      </c>
+      <c r="D92" s="2">
+        <v>5</v>
+      </c>
+      <c r="E92" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="F92" s="7" t="str">
+        <f>VLOOKUP(B92,Sheet2!$G$2:$H$28,2,FALSE)</f>
+        <v>서해구청역</v>
+      </c>
+      <c r="G92" s="2" t="str">
+        <f t="shared" si="14"/>
+        <v>210ES005</v>
+      </c>
+      <c r="H92" s="7" t="s">
+        <v>133</v>
+      </c>
+      <c r="I92" s="7" t="s">
+        <v>377</v>
+      </c>
+      <c r="J92" s="7" t="str">
+        <f t="shared" si="15"/>
+        <v>210ZONE06</v>
+      </c>
+      <c r="K92" s="7" t="str">
+        <f t="shared" si="16"/>
+        <v>https://2line.pages.dev/?id=210ES005,210ES005</v>
+      </c>
+      <c r="L92" s="3" t="s">
+        <v>392</v>
+      </c>
+    </row>
+    <row r="93" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A93" s="7">
+        <f t="shared" si="5"/>
+        <v>92</v>
+      </c>
+      <c r="B93" s="7">
+        <v>210</v>
+      </c>
+      <c r="C93" s="7" t="s">
+        <v>276</v>
+      </c>
+      <c r="D93" s="2">
+        <v>6</v>
+      </c>
+      <c r="E93" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="F93" s="7" t="str">
+        <f>VLOOKUP(B93,Sheet2!$G$2:$H$28,2,FALSE)</f>
+        <v>서해구청역</v>
+      </c>
+      <c r="G93" s="2" t="str">
+        <f t="shared" si="14"/>
+        <v>210ES006</v>
+      </c>
+      <c r="H93" s="7" t="s">
+        <v>134</v>
+      </c>
+      <c r="I93" s="7" t="s">
+        <v>377</v>
+      </c>
+      <c r="J93" s="7" t="str">
+        <f t="shared" si="15"/>
+        <v>210ZONE04</v>
+      </c>
+      <c r="K93" s="7" t="str">
+        <f t="shared" si="16"/>
+        <v>https://2line.pages.dev/?id=210ES006,210ES006</v>
+      </c>
+      <c r="L93" s="3" t="s">
+        <v>393</v>
+      </c>
+    </row>
+    <row r="94" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A94" s="7">
+        <f t="shared" si="5"/>
+        <v>93</v>
+      </c>
+      <c r="B94" s="7">
+        <v>210</v>
+      </c>
+      <c r="C94" s="7" t="s">
+        <v>276</v>
+      </c>
+      <c r="D94" s="2">
+        <v>7</v>
+      </c>
+      <c r="E94" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="F94" s="7" t="str">
+        <f>VLOOKUP(B94,Sheet2!$G$2:$H$28,2,FALSE)</f>
+        <v>서해구청역</v>
+      </c>
+      <c r="G94" s="2" t="str">
+        <f t="shared" si="14"/>
+        <v>210ES007</v>
+      </c>
+      <c r="H94" s="7" t="s">
+        <v>135</v>
+      </c>
+      <c r="I94" s="7" t="s">
+        <v>377</v>
+      </c>
+      <c r="J94" s="7" t="str">
+        <f t="shared" si="15"/>
+        <v>210ZONE01</v>
+      </c>
+      <c r="K94" s="7" t="str">
+        <f t="shared" si="16"/>
+        <v>https://2line.pages.dev/?id=210ES007,210ES007</v>
+      </c>
+      <c r="L94" s="3" t="s">
+        <v>394</v>
+      </c>
+    </row>
+    <row r="95" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A95" s="7">
+        <f t="shared" si="5"/>
+        <v>94</v>
+      </c>
+      <c r="B95" s="7">
+        <v>210</v>
+      </c>
+      <c r="C95" s="7" t="s">
+        <v>276</v>
+      </c>
+      <c r="D95" s="2">
+        <v>8</v>
+      </c>
+      <c r="E95" s="7" t="s">
+        <v>19</v>
+      </c>
+      <c r="F95" s="7" t="str">
+        <f>VLOOKUP(B95,Sheet2!$G$2:$H$28,2,FALSE)</f>
+        <v>서해구청역</v>
+      </c>
+      <c r="G95" s="2" t="str">
+        <f t="shared" si="14"/>
+        <v>210ES008</v>
+      </c>
+      <c r="H95" s="7" t="s">
+        <v>136</v>
+      </c>
+      <c r="I95" s="7" t="s">
+        <v>377</v>
+      </c>
+      <c r="J95" s="7" t="str">
+        <f t="shared" si="15"/>
+        <v>210ZONE01</v>
+      </c>
+      <c r="K95" s="7" t="str">
+        <f t="shared" si="16"/>
+        <v>https://2line.pages.dev/?id=210ES008,210ES008</v>
+      </c>
+      <c r="L95" s="3" t="s">
+        <v>395</v>
+      </c>
+    </row>
+    <row r="96" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A96" s="7">
+        <f t="shared" si="5"/>
+        <v>95</v>
+      </c>
+      <c r="B96" s="7">
+        <v>210</v>
+      </c>
+      <c r="C96" s="7" t="s">
+        <v>276</v>
+      </c>
+      <c r="D96" s="2">
+        <v>9</v>
+      </c>
+      <c r="E96" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="F96" s="7" t="str">
+        <f>VLOOKUP(B96,Sheet2!$G$2:$H$28,2,FALSE)</f>
+        <v>서해구청역</v>
+      </c>
+      <c r="G96" s="2" t="str">
+        <f t="shared" si="14"/>
+        <v>210ES009</v>
+      </c>
+      <c r="H96" s="7" t="s">
+        <v>137</v>
+      </c>
+      <c r="I96" s="7" t="s">
+        <v>377</v>
+      </c>
+      <c r="J96" s="7" t="str">
+        <f t="shared" si="15"/>
+        <v>210ZONE03</v>
+      </c>
+      <c r="K96" s="7" t="str">
+        <f t="shared" si="16"/>
+        <v>https://2line.pages.dev/?id=210ES009,210ES009</v>
+      </c>
+      <c r="L96" s="3" t="s">
+        <v>396</v>
+      </c>
+    </row>
+    <row r="97" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A97" s="7">
+        <f t="shared" si="5"/>
+        <v>96</v>
+      </c>
+      <c r="B97" s="7">
+        <v>210</v>
+      </c>
+      <c r="C97" s="7" t="s">
+        <v>276</v>
+      </c>
+      <c r="D97" s="2">
+        <v>10</v>
+      </c>
+      <c r="E97" s="7" t="s">
+        <v>23</v>
+      </c>
+      <c r="F97" s="7" t="str">
+        <f>VLOOKUP(B97,Sheet2!$G$2:$H$28,2,FALSE)</f>
+        <v>서해구청역</v>
+      </c>
+      <c r="G97" s="2" t="str">
+        <f t="shared" si="14"/>
+        <v>210ES010</v>
+      </c>
+      <c r="H97" s="7" t="s">
+        <v>138</v>
+      </c>
+      <c r="I97" s="7" t="s">
+        <v>377</v>
+      </c>
+      <c r="J97" s="7" t="str">
+        <f t="shared" si="15"/>
+        <v>210ZONE03</v>
+      </c>
+      <c r="K97" s="7" t="str">
+        <f t="shared" si="16"/>
+        <v>https://2line.pages.dev/?id=210ES010,210ES010</v>
+      </c>
+      <c r="L97" s="3" t="s">
+        <v>397</v>
+      </c>
+    </row>
+    <row r="98" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A98" s="7">
+        <f t="shared" si="5"/>
+        <v>97</v>
+      </c>
+      <c r="B98" s="7">
+        <v>210</v>
+      </c>
+      <c r="C98" s="1" t="s">
+        <v>278</v>
+      </c>
+      <c r="D98" s="2">
+        <v>1</v>
+      </c>
+      <c r="E98" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="F98" s="7" t="str">
+        <f>VLOOKUP(B98,Sheet2!$G$2:$H$28,2,FALSE)</f>
+        <v>서해구청역</v>
+      </c>
+      <c r="G98" s="2" t="str">
+        <f t="shared" si="14"/>
+        <v>210EL001</v>
+      </c>
+      <c r="H98" s="7" t="s">
+        <v>379</v>
+      </c>
+      <c r="I98" s="7" t="s">
+        <v>377</v>
+      </c>
+      <c r="J98" s="7" t="str">
+        <f t="shared" si="15"/>
+        <v>210ZONE07</v>
+      </c>
+      <c r="K98" s="7" t="str">
+        <f t="shared" si="16"/>
+        <v>https://2line.pages.dev/?id=210EL001,210EL001</v>
+      </c>
+      <c r="L98" s="3" t="s">
+        <v>398</v>
+      </c>
+    </row>
+    <row r="99" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A99" s="7">
+        <f t="shared" si="5"/>
+        <v>98</v>
+      </c>
+      <c r="B99" s="7">
+        <v>210</v>
+      </c>
+      <c r="C99" s="7" t="s">
+        <v>278</v>
+      </c>
+      <c r="D99" s="2">
+        <v>2</v>
+      </c>
+      <c r="E99" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="F99" s="7" t="str">
+        <f>VLOOKUP(B99,Sheet2!$G$2:$H$28,2,FALSE)</f>
+        <v>서해구청역</v>
+      </c>
+      <c r="G99" s="2" t="str">
+        <f t="shared" si="14"/>
+        <v>210EL002</v>
+      </c>
+      <c r="H99" s="7" t="s">
+        <v>380</v>
+      </c>
+      <c r="I99" s="7" t="s">
+        <v>377</v>
+      </c>
+      <c r="J99" s="7" t="str">
+        <f t="shared" si="15"/>
+        <v>210ZONE08</v>
+      </c>
+      <c r="K99" s="7" t="str">
+        <f t="shared" si="16"/>
+        <v>https://2line.pages.dev/?id=210EL002,210EL002</v>
+      </c>
+      <c r="L99" s="3" t="s">
+        <v>399</v>
+      </c>
+    </row>
+    <row r="100" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A100" s="7">
+        <f t="shared" si="5"/>
+        <v>99</v>
+      </c>
+      <c r="B100" s="7">
+        <v>210</v>
+      </c>
+      <c r="C100" s="7" t="s">
+        <v>278</v>
+      </c>
+      <c r="D100" s="2">
+        <v>3</v>
+      </c>
+      <c r="E100" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="F100" s="7" t="str">
+        <f>VLOOKUP(B100,Sheet2!$G$2:$H$28,2,FALSE)</f>
+        <v>서해구청역</v>
+      </c>
+      <c r="G100" s="2" t="str">
+        <f t="shared" si="14"/>
+        <v>210EL003</v>
+      </c>
+      <c r="H100" s="7" t="s">
+        <v>381</v>
+      </c>
+      <c r="I100" s="7" t="s">
+        <v>377</v>
+      </c>
+      <c r="J100" s="7" t="str">
+        <f t="shared" si="15"/>
+        <v>210ZONE01</v>
+      </c>
+      <c r="K100" s="7" t="str">
+        <f t="shared" si="16"/>
+        <v>https://2line.pages.dev/?id=210EL003,210EL003</v>
+      </c>
+      <c r="L100" s="3" t="s">
+        <v>400</v>
+      </c>
+    </row>
+    <row r="101" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A101" s="7">
+        <f t="shared" si="5"/>
+        <v>100</v>
+      </c>
+      <c r="B101" s="7">
+        <v>210</v>
+      </c>
+      <c r="C101" s="7" t="s">
+        <v>278</v>
+      </c>
+      <c r="D101" s="2">
+        <v>4</v>
+      </c>
+      <c r="E101" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="F101" s="7" t="str">
+        <f>VLOOKUP(B101,Sheet2!$G$2:$H$28,2,FALSE)</f>
+        <v>서해구청역</v>
+      </c>
+      <c r="G101" s="2" t="str">
+        <f t="shared" si="14"/>
+        <v>210EL004</v>
+      </c>
+      <c r="H101" s="7" t="s">
+        <v>382</v>
+      </c>
+      <c r="I101" s="7" t="s">
+        <v>377</v>
+      </c>
+      <c r="J101" s="7" t="str">
+        <f t="shared" si="15"/>
+        <v>210ZONE02</v>
+      </c>
+      <c r="K101" s="7" t="str">
+        <f t="shared" si="16"/>
+        <v>https://2line.pages.dev/?id=210EL004,210EL004</v>
+      </c>
+      <c r="L101" s="3" t="s">
+        <v>401</v>
       </c>
     </row>
   </sheetData>
@@ -5585,9 +6321,28 @@
     <hyperlink ref="L80" r:id="rId79" xr:uid="{203B0D94-065B-4033-A07B-261A16268CFD}"/>
     <hyperlink ref="L81" r:id="rId80" xr:uid="{660AE8F0-E818-4BF0-A9C1-97AF576BD02A}"/>
     <hyperlink ref="L82" r:id="rId81" xr:uid="{C3AB159B-152A-47A0-B758-229F168159A4}"/>
+    <hyperlink ref="L83" r:id="rId82" xr:uid="{CDA4D126-CE9F-4575-98F5-47FB51D0F9DF}"/>
+    <hyperlink ref="L84" r:id="rId83" xr:uid="{7A5A4F79-A3B2-4A50-8B8B-1A784BD7E52B}"/>
+    <hyperlink ref="L85" r:id="rId84" xr:uid="{C38E6753-E8D0-49DA-857B-0097508CBFD0}"/>
+    <hyperlink ref="L86" r:id="rId85" xr:uid="{F149D0EA-F181-43E6-BF28-C1C714895D93}"/>
+    <hyperlink ref="L87" r:id="rId86" xr:uid="{5A6F7379-250D-4E93-93DF-312759A05A2C}"/>
+    <hyperlink ref="L88" r:id="rId87" xr:uid="{720323A6-80F2-49A3-8530-0FD2183A904F}"/>
+    <hyperlink ref="L89" r:id="rId88" xr:uid="{E2BF65CD-79D1-4AA5-B91D-549A163C86B9}"/>
+    <hyperlink ref="L90" r:id="rId89" xr:uid="{A5601B0D-66E7-452D-893A-04D1B660EDB0}"/>
+    <hyperlink ref="L91" r:id="rId90" xr:uid="{FB2682D3-0660-42D9-BB31-C55BBED3B8C0}"/>
+    <hyperlink ref="L92" r:id="rId91" xr:uid="{8EAA5432-2010-4FAB-8FBC-497888E32827}"/>
+    <hyperlink ref="L93" r:id="rId92" xr:uid="{F3FAAAA7-0BD4-4374-9267-5E4BC010B11E}"/>
+    <hyperlink ref="L94" r:id="rId93" xr:uid="{928B81D5-B2D5-47E9-8837-D4819B783514}"/>
+    <hyperlink ref="L95" r:id="rId94" xr:uid="{084C3E1C-CCE7-41FF-AFA3-51EAB719C4B1}"/>
+    <hyperlink ref="L96" r:id="rId95" xr:uid="{6D9ACF20-85EF-452D-96FB-EB588E9A8CBC}"/>
+    <hyperlink ref="L97" r:id="rId96" xr:uid="{E41961CE-4E7B-4001-8FA7-AD065A4C7514}"/>
+    <hyperlink ref="L98" r:id="rId97" xr:uid="{B4BDCC83-883F-41DD-B485-B7A20C5A3772}"/>
+    <hyperlink ref="L99" r:id="rId98" xr:uid="{411F2A0C-32B4-4D87-8641-BC43A0AA3204}"/>
+    <hyperlink ref="L100" r:id="rId99" xr:uid="{2AB477BE-F512-458C-AFFA-BB678605C7FE}"/>
+    <hyperlink ref="L101" r:id="rId100" xr:uid="{0D479A27-9741-4CFD-B82E-58D70EEEDBAF}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" r:id="rId82"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId101"/>
 </worksheet>
 </file>
 
@@ -5621,10 +6376,10 @@
       <c r="E1" s="1" t="s">
         <v>180</v>
       </c>
-      <c r="G1" s="7" t="s">
+      <c r="G1" s="8" t="s">
         <v>225</v>
       </c>
-      <c r="H1" s="7"/>
+      <c r="H1" s="8"/>
     </row>
     <row r="2" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A2" s="1" t="s">
